--- a/frontend/public/SPOT_3way_analysis_40quotes.xlsx
+++ b/frontend/public/SPOT_3way_analysis_40quotes.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +46,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +71,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,20 +130,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -214,7 +258,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Actual invoice vs iQuote sell vs SPOT sell — 40 produced jobs</a:t>
+              <a:t>Actual invoice vs iQuote sell vs SPOT sell — 40 jobs (outliers tinted)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -375,7 +419,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Estimated COST vs actual by category — 40 produced jobs</a:t>
+              <a:t>Estimated COST vs actual by category — CLEAN 35 jobs (outliers excluded)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -390,7 +434,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Charts -comparing to actuals'!B47</f>
+              <f>'Charts -comparing to actuals'!E48</f>
             </strRef>
           </tx>
           <spPr>
@@ -400,12 +444,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts -comparing to actuals'!$A$48:$A$52</f>
+              <f>'Charts -comparing to actuals'!$A$49:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts -comparing to actuals'!$B$48:$B$52</f>
+              <f>'Charts -comparing to actuals'!$E$49:$E$53</f>
             </numRef>
           </val>
         </ser>
@@ -414,7 +458,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Charts -comparing to actuals'!C47</f>
+              <f>'Charts -comparing to actuals'!F48</f>
             </strRef>
           </tx>
           <spPr>
@@ -424,12 +468,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts -comparing to actuals'!$A$48:$A$52</f>
+              <f>'Charts -comparing to actuals'!$A$49:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts -comparing to actuals'!$C$48:$C$52</f>
+              <f>'Charts -comparing to actuals'!$F$49:$F$53</f>
             </numRef>
           </val>
         </ser>
@@ -438,7 +482,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Charts -comparing to actuals'!D47</f>
+              <f>'Charts -comparing to actuals'!G48</f>
             </strRef>
           </tx>
           <spPr>
@@ -448,12 +492,173 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Charts -comparing to actuals'!$A$48:$A$52</f>
+              <f>'Charts -comparing to actuals'!$A$49:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Charts -comparing to actuals'!$D$48:$D$52</f>
+              <f>'Charts -comparing to actuals'!$G$49:$G$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Category</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Cost $</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Estimated COST vs actual by category — ALL 40 jobs (for reference)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts -comparing to actuals'!B48</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts -comparing to actuals'!$A$49:$A$53</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts -comparing to actuals'!$B$49:$B$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts -comparing to actuals'!C48</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts -comparing to actuals'!$A$49:$A$53</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts -comparing to actuals'!$C$49:$C$53</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts -comparing to actuals'!D48</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts -comparing to actuals'!$A$49:$A$53</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts -comparing to actuals'!$D$49:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -527,7 +732,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>8</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -549,9 +754,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>8</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="12960000" cy="5760000"/>
@@ -564,6 +769,28 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="12960000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -861,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I284"/>
+  <dimension ref="A1:J291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -872,7 +1099,8 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -932,6 +1160,11 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>Outlier?</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
@@ -969,6 +1202,8 @@
           <t>-8%</t>
         </is>
       </c>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -997,6 +1232,7 @@
           <t>+139%</t>
         </is>
       </c>
+      <c r="I6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1025,6 +1261,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1053,6 +1290,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1081,39 +1319,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>799.1799999999999</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <v>635.75</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="10" t="n">
         <v>300.49</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>+166%</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>+112%</t>
         </is>
       </c>
-      <c r="I10" s="11" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1148,6 +1389,8 @@
           <t>-22%</t>
         </is>
       </c>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -1176,6 +1419,7 @@
           <t>-65%</t>
         </is>
       </c>
+      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1204,6 +1448,7 @@
           <t>-32%</t>
         </is>
       </c>
+      <c r="I14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1232,6 +1477,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -1260,39 +1506,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="10" t="n">
         <v>2133.1</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="10" t="n">
         <v>1468.32</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="10" t="n">
         <v>2677.09</v>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>-20%</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>-45%</t>
         </is>
       </c>
-      <c r="I17" s="11" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1327,6 +1576,8 @@
           <t>-8%</t>
         </is>
       </c>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -1355,6 +1606,7 @@
           <t>-61%</t>
         </is>
       </c>
+      <c r="I20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -1383,6 +1635,7 @@
           <t>-55%</t>
         </is>
       </c>
+      <c r="I21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -1411,6 +1664,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -1439,39 +1693,42 @@
           <t>-100%</t>
         </is>
       </c>
+      <c r="I23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="10" t="n">
         <v>1100.69</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>1615.53</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="10" t="n">
         <v>1580.44</v>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>-30%</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>+2%</t>
         </is>
       </c>
-      <c r="I24" s="11" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1506,6 +1763,8 @@
           <t>+3%</t>
         </is>
       </c>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -1534,6 +1793,7 @@
           <t>+10%</t>
         </is>
       </c>
+      <c r="I27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -1562,6 +1822,7 @@
           <t>-54%</t>
         </is>
       </c>
+      <c r="I28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -1590,6 +1851,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -1618,39 +1880,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="n"/>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="10" t="n">
         <v>4420.9</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="10" t="n">
         <v>2781.63</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="10" t="n">
         <v>2452.37</v>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>+80%</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>+13%</t>
         </is>
       </c>
-      <c r="I31" s="11" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1685,6 +1950,8 @@
           <t>-0%</t>
         </is>
       </c>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="8" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -1713,6 +1980,7 @@
           <t>-28%</t>
         </is>
       </c>
+      <c r="I34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -1741,6 +2009,7 @@
           <t>-39%</t>
         </is>
       </c>
+      <c r="I35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -1769,6 +2038,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -1797,39 +2067,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="10" t="n">
         <v>344.63</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>285.32</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>398.47</v>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>-14%</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>-28%</t>
         </is>
       </c>
-      <c r="I38" s="11" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -1864,6 +2137,8 @@
           <t>-8%</t>
         </is>
       </c>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1892,6 +2167,7 @@
           <t>-2%</t>
         </is>
       </c>
+      <c r="I41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1920,6 +2196,7 @@
           <t>-75%</t>
         </is>
       </c>
+      <c r="I42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1948,6 +2225,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1976,39 +2254,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D45" s="10" t="n">
         <v>1891.23</v>
       </c>
-      <c r="E45" s="9" t="n">
+      <c r="E45" s="10" t="n">
         <v>1189.89</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="10" t="n">
         <v>2278.07</v>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>-17%</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>-48%</t>
         </is>
       </c>
-      <c r="I45" s="11" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2043,6 +2324,8 @@
           <t>-8%</t>
         </is>
       </c>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="8" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -2071,6 +2354,7 @@
           <t>-29%</t>
         </is>
       </c>
+      <c r="I48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -2099,6 +2383,7 @@
           <t>-64%</t>
         </is>
       </c>
+      <c r="I49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -2127,6 +2412,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -2155,39 +2441,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I51" s="5" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="n"/>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="D52" s="10" t="n">
         <v>793.12</v>
       </c>
-      <c r="E52" s="9" t="n">
+      <c r="E52" s="10" t="n">
         <v>618.5</v>
       </c>
-      <c r="F52" s="9" t="n">
+      <c r="F52" s="10" t="n">
         <v>1019.14</v>
       </c>
-      <c r="G52" s="10" t="inlineStr">
+      <c r="G52" s="11" t="inlineStr">
         <is>
           <t>-22%</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>-39%</t>
         </is>
       </c>
-      <c r="I52" s="11" t="n"/>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
+      <c r="I53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2222,6 +2511,8 @@
           <t>-8%</t>
         </is>
       </c>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="8" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -2250,6 +2541,7 @@
           <t>-21%</t>
         </is>
       </c>
+      <c r="I55" s="5" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n"/>
@@ -2278,6 +2570,7 @@
           <t>-43%</t>
         </is>
       </c>
+      <c r="I56" s="5" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n"/>
@@ -2306,6 +2599,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I57" s="5" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -2334,39 +2628,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I58" s="5" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D59" s="9" t="n">
+      <c r="D59" s="10" t="n">
         <v>1154.26</v>
       </c>
-      <c r="E59" s="9" t="n">
+      <c r="E59" s="10" t="n">
         <v>914.03</v>
       </c>
-      <c r="F59" s="9" t="n">
+      <c r="F59" s="10" t="n">
         <v>1211.19</v>
       </c>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr">
         <is>
           <t>-5%</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H59" s="11" t="inlineStr">
         <is>
           <t>-25%</t>
         </is>
       </c>
-      <c r="I59" s="11" t="n"/>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -2401,6 +2698,8 @@
           <t>+53%</t>
         </is>
       </c>
+      <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="8" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -2429,6 +2728,7 @@
           <t>-52%</t>
         </is>
       </c>
+      <c r="I62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -2457,6 +2757,7 @@
           <t>+27%</t>
         </is>
       </c>
+      <c r="I63" s="5" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -2485,6 +2786,7 @@
           <t>+19%</t>
         </is>
       </c>
+      <c r="I64" s="5" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>
@@ -2513,39 +2815,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I65" s="5" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="n"/>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="A66" s="9" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D66" s="9" t="n">
+      <c r="D66" s="10" t="n">
         <v>3004.68</v>
       </c>
-      <c r="E66" s="9" t="n">
+      <c r="E66" s="10" t="n">
         <v>2839.28</v>
       </c>
-      <c r="F66" s="9" t="n">
+      <c r="F66" s="10" t="n">
         <v>2687.42</v>
       </c>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G66" s="11" t="inlineStr">
         <is>
           <t>+12%</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="11" t="inlineStr">
         <is>
           <t>+6%</t>
         </is>
       </c>
-      <c r="I66" s="11" t="n"/>
+      <c r="I66" s="9" t="n"/>
+      <c r="J66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -2580,6 +2885,8 @@
           <t>-13%</t>
         </is>
       </c>
+      <c r="I68" s="7" t="inlineStr"/>
+      <c r="J68" s="8" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n"/>
@@ -2608,6 +2915,7 @@
           <t>-32%</t>
         </is>
       </c>
+      <c r="I69" s="5" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -2636,6 +2944,7 @@
           <t>-20%</t>
         </is>
       </c>
+      <c r="I70" s="5" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -2664,6 +2973,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I71" s="5" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n"/>
@@ -2692,39 +3002,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="8" t="n"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D73" s="9" t="n">
+      <c r="D73" s="10" t="n">
         <v>1752.98</v>
       </c>
-      <c r="E73" s="9" t="n">
+      <c r="E73" s="10" t="n">
         <v>1651.78</v>
       </c>
-      <c r="F73" s="9" t="n">
+      <c r="F73" s="10" t="n">
         <v>2148.89</v>
       </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
         <is>
           <t>-18%</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H73" s="11" t="inlineStr">
         <is>
           <t>-23%</t>
         </is>
       </c>
-      <c r="I73" s="11" t="n"/>
+      <c r="I73" s="9" t="n"/>
+      <c r="J73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -2759,6 +3072,8 @@
           <t>+37%</t>
         </is>
       </c>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="8" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n"/>
@@ -2787,6 +3102,7 @@
           <t>-73%</t>
         </is>
       </c>
+      <c r="I76" s="5" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n"/>
@@ -2815,6 +3131,7 @@
           <t>+92%</t>
         </is>
       </c>
+      <c r="I77" s="5" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -2843,6 +3160,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I78" s="5" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -2871,39 +3189,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I79" s="5" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="n"/>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D80" s="9" t="n">
+      <c r="D80" s="10" t="n">
         <v>441.87</v>
       </c>
-      <c r="E80" s="9" t="n">
+      <c r="E80" s="10" t="n">
         <v>562.01</v>
       </c>
-      <c r="F80" s="9" t="n">
+      <c r="F80" s="10" t="n">
         <v>793.4400000000001</v>
       </c>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="G80" s="11" t="inlineStr">
         <is>
           <t>-44%</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="H80" s="11" t="inlineStr">
         <is>
           <t>-29%</t>
         </is>
       </c>
-      <c r="I80" s="11" t="n"/>
+      <c r="I80" s="9" t="n"/>
+      <c r="J80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
+      <c r="I81" s="5" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -2938,6 +3259,8 @@
           <t>-14%</t>
         </is>
       </c>
+      <c r="I82" s="7" t="inlineStr"/>
+      <c r="J82" s="8" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -2966,6 +3289,7 @@
           <t>-50%</t>
         </is>
       </c>
+      <c r="I83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n"/>
@@ -2994,6 +3318,7 @@
           <t>-58%</t>
         </is>
       </c>
+      <c r="I84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -3022,6 +3347,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n"/>
@@ -3050,39 +3376,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="8" t="n"/>
-      <c r="B87" s="8" t="n"/>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D87" s="9" t="n">
+      <c r="D87" s="10" t="n">
         <v>457.93</v>
       </c>
-      <c r="E87" s="9" t="n">
+      <c r="E87" s="10" t="n">
         <v>367.61</v>
       </c>
-      <c r="F87" s="9" t="n">
+      <c r="F87" s="10" t="n">
         <v>567.36</v>
       </c>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
         <is>
           <t>-19%</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="H87" s="11" t="inlineStr">
         <is>
           <t>-35%</t>
         </is>
       </c>
-      <c r="I87" s="11" t="n"/>
+      <c r="I87" s="9" t="n"/>
+      <c r="J87" s="12" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
+      <c r="I88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -3117,6 +3446,8 @@
           <t>+14%</t>
         </is>
       </c>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="8" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n"/>
@@ -3145,6 +3476,7 @@
           <t>-56%</t>
         </is>
       </c>
+      <c r="I90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n"/>
@@ -3173,6 +3505,7 @@
           <t>-59%</t>
         </is>
       </c>
+      <c r="I91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n"/>
@@ -3201,6 +3534,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -3229,39 +3563,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="8" t="n"/>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D94" s="9" t="n">
+      <c r="D94" s="10" t="n">
         <v>557.2</v>
       </c>
-      <c r="E94" s="9" t="n">
+      <c r="E94" s="10" t="n">
         <v>478.44</v>
       </c>
-      <c r="F94" s="9" t="n">
+      <c r="F94" s="10" t="n">
         <v>904.79</v>
       </c>
-      <c r="G94" s="10" t="inlineStr">
+      <c r="G94" s="11" t="inlineStr">
         <is>
           <t>-38%</t>
         </is>
       </c>
-      <c r="H94" s="10" t="inlineStr">
+      <c r="H94" s="11" t="inlineStr">
         <is>
           <t>-47%</t>
         </is>
       </c>
-      <c r="I94" s="11" t="n"/>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="12" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -3296,6 +3633,8 @@
           <t>+1%</t>
         </is>
       </c>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="8" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n"/>
@@ -3324,6 +3663,7 @@
           <t>-65%</t>
         </is>
       </c>
+      <c r="I97" s="5" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n"/>
@@ -3352,6 +3692,7 @@
           <t>-4%</t>
         </is>
       </c>
+      <c r="I98" s="5" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n"/>
@@ -3380,6 +3721,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I99" s="5" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n"/>
@@ -3408,39 +3750,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I100" s="5" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="8" t="n"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="inlineStr">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D101" s="9" t="n">
+      <c r="D101" s="10" t="n">
         <v>442.62</v>
       </c>
-      <c r="E101" s="9" t="n">
+      <c r="E101" s="10" t="n">
         <v>369.78</v>
       </c>
-      <c r="F101" s="9" t="n">
+      <c r="F101" s="10" t="n">
         <v>477.54</v>
       </c>
-      <c r="G101" s="10" t="inlineStr">
+      <c r="G101" s="11" t="inlineStr">
         <is>
           <t>-7%</t>
         </is>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H101" s="11" t="inlineStr">
         <is>
           <t>-23%</t>
         </is>
       </c>
-      <c r="I101" s="11" t="n"/>
+      <c r="I101" s="9" t="n"/>
+      <c r="J101" s="12" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
+      <c r="I102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -3475,6 +3820,8 @@
           <t>-0%</t>
         </is>
       </c>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="8" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n"/>
@@ -3503,6 +3850,7 @@
           <t>-47%</t>
         </is>
       </c>
+      <c r="I104" s="5" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n"/>
@@ -3531,6 +3879,7 @@
           <t>-61%</t>
         </is>
       </c>
+      <c r="I105" s="5" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n"/>
@@ -3559,6 +3908,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n"/>
@@ -3587,39 +3937,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I107" s="5" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="8" t="n"/>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D108" s="9" t="n">
+      <c r="D108" s="10" t="n">
         <v>389.89</v>
       </c>
-      <c r="E108" s="9" t="n">
+      <c r="E108" s="10" t="n">
         <v>305.4</v>
       </c>
-      <c r="F108" s="9" t="n">
+      <c r="F108" s="10" t="n">
         <v>505.78</v>
       </c>
-      <c r="G108" s="10" t="inlineStr">
+      <c r="G108" s="11" t="inlineStr">
         <is>
           <t>-23%</t>
         </is>
       </c>
-      <c r="H108" s="10" t="inlineStr">
+      <c r="H108" s="11" t="inlineStr">
         <is>
           <t>-40%</t>
         </is>
       </c>
-      <c r="I108" s="11" t="n"/>
+      <c r="I108" s="9" t="n"/>
+      <c r="J108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
+      <c r="I109" s="5" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -3654,6 +4007,8 @@
           <t>-21%</t>
         </is>
       </c>
+      <c r="I110" s="7" t="inlineStr"/>
+      <c r="J110" s="8" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n"/>
@@ -3682,6 +4037,7 @@
           <t>-61%</t>
         </is>
       </c>
+      <c r="I111" s="5" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -3710,6 +4066,7 @@
           <t>-54%</t>
         </is>
       </c>
+      <c r="I112" s="5" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -3738,6 +4095,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I113" s="5" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n"/>
@@ -3766,39 +4124,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I114" s="5" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="n"/>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="n"/>
+      <c r="C115" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D115" s="9" t="n">
+      <c r="D115" s="10" t="n">
         <v>480</v>
       </c>
-      <c r="E115" s="9" t="n">
+      <c r="E115" s="10" t="n">
         <v>374.57</v>
       </c>
-      <c r="F115" s="9" t="n">
+      <c r="F115" s="10" t="n">
         <v>685.33</v>
       </c>
-      <c r="G115" s="10" t="inlineStr">
+      <c r="G115" s="11" t="inlineStr">
         <is>
           <t>-30%</t>
         </is>
       </c>
-      <c r="H115" s="10" t="inlineStr">
+      <c r="H115" s="11" t="inlineStr">
         <is>
           <t>-45%</t>
         </is>
       </c>
-      <c r="I115" s="11" t="n"/>
+      <c r="I115" s="9" t="n"/>
+      <c r="J115" s="12" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
+      <c r="I116" s="5" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="n">
@@ -3833,6 +4194,8 @@
           <t>-21%</t>
         </is>
       </c>
+      <c r="I117" s="7" t="inlineStr"/>
+      <c r="J117" s="8" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -3861,6 +4224,7 @@
           <t>-46%</t>
         </is>
       </c>
+      <c r="I118" s="5" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n"/>
@@ -3889,6 +4253,7 @@
           <t>+60%</t>
         </is>
       </c>
+      <c r="I119" s="5" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n"/>
@@ -3917,6 +4282,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I120" s="5" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n"/>
@@ -3945,39 +4311,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I121" s="5" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="n"/>
-      <c r="B122" s="8" t="n"/>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D122" s="9" t="n">
+      <c r="D122" s="10" t="n">
         <v>2014.99</v>
       </c>
-      <c r="E122" s="9" t="n">
+      <c r="E122" s="10" t="n">
         <v>2051.47</v>
       </c>
-      <c r="F122" s="9" t="n">
+      <c r="F122" s="10" t="n">
         <v>2343.9</v>
       </c>
-      <c r="G122" s="10" t="inlineStr">
+      <c r="G122" s="11" t="inlineStr">
         <is>
           <t>-14%</t>
         </is>
       </c>
-      <c r="H122" s="10" t="inlineStr">
+      <c r="H122" s="11" t="inlineStr">
         <is>
           <t>-12%</t>
         </is>
       </c>
-      <c r="I122" s="11" t="n"/>
+      <c r="I122" s="9" t="n"/>
+      <c r="J122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
+      <c r="I123" s="5" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="n">
@@ -4012,6 +4381,8 @@
           <t>+0%</t>
         </is>
       </c>
+      <c r="I124" s="7" t="inlineStr"/>
+      <c r="J124" s="8" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n"/>
@@ -4040,6 +4411,7 @@
           <t>-44%</t>
         </is>
       </c>
+      <c r="I125" s="5" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n"/>
@@ -4068,6 +4440,7 @@
           <t>+34%</t>
         </is>
       </c>
+      <c r="I126" s="5" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n"/>
@@ -4096,6 +4469,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I127" s="5" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n"/>
@@ -4124,39 +4498,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I128" s="5" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="n"/>
-      <c r="B129" s="8" t="n"/>
-      <c r="C129" s="8" t="inlineStr">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="9" t="n"/>
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D129" s="9" t="n">
+      <c r="D129" s="10" t="n">
         <v>444.32</v>
       </c>
-      <c r="E129" s="9" t="n">
+      <c r="E129" s="10" t="n">
         <v>540.61</v>
       </c>
-      <c r="F129" s="9" t="n">
+      <c r="F129" s="10" t="n">
         <v>537.79</v>
       </c>
-      <c r="G129" s="10" t="inlineStr">
+      <c r="G129" s="11" t="inlineStr">
         <is>
           <t>-17%</t>
         </is>
       </c>
-      <c r="H129" s="10" t="inlineStr">
+      <c r="H129" s="11" t="inlineStr">
         <is>
           <t>+1%</t>
         </is>
       </c>
-      <c r="I129" s="11" t="n"/>
+      <c r="I129" s="9" t="n"/>
+      <c r="J129" s="12" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
+      <c r="I130" s="5" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="n">
@@ -4191,6 +4568,8 @@
           <t>+7%</t>
         </is>
       </c>
+      <c r="I131" s="7" t="inlineStr"/>
+      <c r="J131" s="8" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n"/>
@@ -4219,6 +4598,7 @@
           <t>-54%</t>
         </is>
       </c>
+      <c r="I132" s="5" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n"/>
@@ -4247,6 +4627,7 @@
           <t>-9%</t>
         </is>
       </c>
+      <c r="I133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n"/>
@@ -4275,6 +4656,7 @@
           <t>-35%</t>
         </is>
       </c>
+      <c r="I134" s="5" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n"/>
@@ -4303,39 +4685,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I135" s="5" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="8" t="n"/>
-      <c r="B136" s="8" t="n"/>
-      <c r="C136" s="8" t="inlineStr">
+      <c r="A136" s="9" t="n"/>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D136" s="9" t="n">
+      <c r="D136" s="10" t="n">
         <v>348.92</v>
       </c>
-      <c r="E136" s="9" t="n">
+      <c r="E136" s="10" t="n">
         <v>325.11</v>
       </c>
-      <c r="F136" s="9" t="n">
+      <c r="F136" s="10" t="n">
         <v>529.17</v>
       </c>
-      <c r="G136" s="10" t="inlineStr">
+      <c r="G136" s="11" t="inlineStr">
         <is>
           <t>-34%</t>
         </is>
       </c>
-      <c r="H136" s="10" t="inlineStr">
+      <c r="H136" s="11" t="inlineStr">
         <is>
           <t>-39%</t>
         </is>
       </c>
-      <c r="I136" s="11" t="n"/>
+      <c r="I136" s="9" t="n"/>
+      <c r="J136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
+      <c r="I137" s="5" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n">
@@ -4370,6 +4755,8 @@
           <t>+1%</t>
         </is>
       </c>
+      <c r="I138" s="7" t="inlineStr"/>
+      <c r="J138" s="8" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n"/>
@@ -4398,6 +4785,7 @@
           <t>-33%</t>
         </is>
       </c>
+      <c r="I139" s="5" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n"/>
@@ -4426,6 +4814,7 @@
           <t>-61%</t>
         </is>
       </c>
+      <c r="I140" s="5" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n"/>
@@ -4454,6 +4843,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n"/>
@@ -4482,39 +4872,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I142" s="5" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="8" t="n"/>
-      <c r="B143" s="8" t="n"/>
-      <c r="C143" s="8" t="inlineStr">
+      <c r="A143" s="9" t="n"/>
+      <c r="B143" s="9" t="n"/>
+      <c r="C143" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D143" s="9" t="n">
+      <c r="D143" s="10" t="n">
         <v>202.47</v>
       </c>
-      <c r="E143" s="9" t="n">
+      <c r="E143" s="10" t="n">
         <v>185.48</v>
       </c>
-      <c r="F143" s="9" t="n">
+      <c r="F143" s="10" t="n">
         <v>326.48</v>
       </c>
-      <c r="G143" s="10" t="inlineStr">
+      <c r="G143" s="11" t="inlineStr">
         <is>
           <t>-38%</t>
         </is>
       </c>
-      <c r="H143" s="10" t="inlineStr">
+      <c r="H143" s="11" t="inlineStr">
         <is>
           <t>-43%</t>
         </is>
       </c>
-      <c r="I143" s="11" t="n"/>
+      <c r="I143" s="9" t="n"/>
+      <c r="J143" s="12" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
+      <c r="I144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
@@ -4525,180 +4918,199 @@
           <t>RW-260807-132828 / 223127</t>
         </is>
       </c>
-      <c r="C145" s="5" t="inlineStr">
+      <c r="C145" s="13" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D145" s="6" t="n">
+      <c r="D145" s="14" t="n">
         <v>1912.52</v>
       </c>
-      <c r="E145" s="6" t="n">
+      <c r="E145" s="14" t="n">
         <v>92.5</v>
       </c>
-      <c r="F145" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I145" s="12" t="inlineStr">
+      <c r="F145" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H145" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J145" s="17" t="inlineStr">
         <is>
           <t>[SPOT] SPOT Buy Min triggered for ECT 32 B 45.25x72 Sheet (663 sheets); [iQuote] Not really sure what happened in production, planned to use 32ect B-Flute Kraft/Kraft 45-1/4 corr x 72, but 0$ material costs or usage found in database?</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n"/>
-      <c r="B146" s="5" t="n"/>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="A146" s="13" t="n"/>
+      <c r="B146" s="13" t="n"/>
+      <c r="C146" s="13" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="D146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H146" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D146" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I146" s="13" t="n"/>
+      <c r="J146" s="18" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n"/>
-      <c r="B147" s="5" t="n"/>
-      <c r="C147" s="5" t="inlineStr">
+      <c r="A147" s="13" t="n"/>
+      <c r="B147" s="13" t="n"/>
+      <c r="C147" s="13" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="D147" s="6" t="n">
+      <c r="D147" s="14" t="n">
         <v>97.52</v>
       </c>
-      <c r="E147" s="6" t="n">
+      <c r="E147" s="14" t="n">
         <v>97.18000000000001</v>
       </c>
-      <c r="F147" s="6" t="n">
+      <c r="F147" s="14" t="n">
         <v>137.76</v>
       </c>
-      <c r="G147" s="7" t="inlineStr">
+      <c r="G147" s="15" t="inlineStr">
         <is>
           <t>-29%</t>
         </is>
       </c>
-      <c r="H147" s="7" t="inlineStr">
+      <c r="H147" s="15" t="inlineStr">
         <is>
           <t>-29%</t>
         </is>
       </c>
+      <c r="I147" s="13" t="n"/>
+      <c r="J147" s="18" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n"/>
-      <c r="B148" s="5" t="n"/>
-      <c r="C148" s="5" t="inlineStr">
+      <c r="A148" s="13" t="n"/>
+      <c r="B148" s="13" t="n"/>
+      <c r="C148" s="13" t="inlineStr">
         <is>
           <t>Handwork</t>
         </is>
       </c>
-      <c r="D148" s="6" t="n">
+      <c r="D148" s="14" t="n">
         <v>17.25</v>
       </c>
-      <c r="E148" s="6" t="n">
+      <c r="E148" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="F148" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H148" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="F148" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I148" s="13" t="n"/>
+      <c r="J148" s="18" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n"/>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="5" t="inlineStr">
+      <c r="A149" s="13" t="n"/>
+      <c r="B149" s="13" t="n"/>
+      <c r="C149" s="13" t="inlineStr">
         <is>
           <t>Die</t>
         </is>
       </c>
-      <c r="D149" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D149" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H149" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I149" s="13" t="n"/>
+      <c r="J149" s="18" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="8" t="n"/>
-      <c r="B150" s="8" t="n"/>
-      <c r="C150" s="8" t="inlineStr">
+      <c r="A150" s="19" t="n"/>
+      <c r="B150" s="19" t="n"/>
+      <c r="C150" s="19" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D150" s="9" t="n">
+      <c r="D150" s="20" t="n">
         <v>2027.29</v>
       </c>
-      <c r="E150" s="9" t="n">
+      <c r="E150" s="20" t="n">
         <v>214.68</v>
       </c>
-      <c r="F150" s="9" t="n">
+      <c r="F150" s="20" t="n">
         <v>137.76</v>
       </c>
-      <c r="G150" s="10" t="inlineStr">
+      <c r="G150" s="21" t="inlineStr">
         <is>
           <t>+1372%</t>
         </is>
       </c>
-      <c r="H150" s="10" t="inlineStr">
+      <c r="H150" s="21" t="inlineStr">
         <is>
           <t>+56%</t>
         </is>
       </c>
-      <c r="I150" s="11" t="n"/>
+      <c r="I150" s="21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J150" s="22" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
+      <c r="I151" s="5" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
@@ -4709,180 +5121,199 @@
           <t>RW-260807-133446 / 223172</t>
         </is>
       </c>
-      <c r="C152" s="5" t="inlineStr">
+      <c r="C152" s="13" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D152" s="6" t="n">
+      <c r="D152" s="14" t="n">
         <v>1913.27</v>
       </c>
-      <c r="E152" s="6" t="n">
+      <c r="E152" s="14" t="n">
         <v>113.6</v>
       </c>
-      <c r="F152" s="6" t="n">
+      <c r="F152" s="14" t="n">
         <v>110.56</v>
       </c>
-      <c r="G152" s="7" t="inlineStr">
+      <c r="G152" s="15" t="inlineStr">
         <is>
           <t>+1631%</t>
         </is>
       </c>
-      <c r="H152" s="7" t="inlineStr">
+      <c r="H152" s="15" t="inlineStr">
         <is>
           <t>+3%</t>
         </is>
       </c>
-      <c r="I152" s="12" t="inlineStr">
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J152" s="17" t="inlineStr">
         <is>
           <t>[SPOT] SPOT Buy Min triggered for ECT 32 SW C 45.25x72 Kraft/Kraft (663 sheets); Actual material was 55x76 in production (50 sheets ordered)</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n"/>
-      <c r="B153" s="5" t="n"/>
-      <c r="C153" s="5" t="inlineStr">
+      <c r="A153" s="13" t="n"/>
+      <c r="B153" s="13" t="n"/>
+      <c r="C153" s="13" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="D153" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D153" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H153" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I153" s="13" t="n"/>
+      <c r="J153" s="18" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n"/>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="5" t="inlineStr">
+      <c r="A154" s="13" t="n"/>
+      <c r="B154" s="13" t="n"/>
+      <c r="C154" s="13" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="D154" s="6" t="n">
+      <c r="D154" s="14" t="n">
         <v>181.26</v>
       </c>
-      <c r="E154" s="6" t="n">
+      <c r="E154" s="14" t="n">
         <v>196.43</v>
       </c>
-      <c r="F154" s="6" t="n">
+      <c r="F154" s="14" t="n">
         <v>201.78</v>
       </c>
-      <c r="G154" s="7" t="inlineStr">
+      <c r="G154" s="15" t="inlineStr">
         <is>
           <t>-10%</t>
         </is>
       </c>
-      <c r="H154" s="7" t="inlineStr">
+      <c r="H154" s="15" t="inlineStr">
         <is>
           <t>-3%</t>
         </is>
       </c>
+      <c r="I154" s="13" t="n"/>
+      <c r="J154" s="18" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n"/>
-      <c r="B155" s="5" t="n"/>
-      <c r="C155" s="5" t="inlineStr">
+      <c r="A155" s="13" t="n"/>
+      <c r="B155" s="13" t="n"/>
+      <c r="C155" s="13" t="inlineStr">
         <is>
           <t>Handwork</t>
         </is>
       </c>
-      <c r="D155" s="6" t="n">
+      <c r="D155" s="14" t="n">
         <v>34.5</v>
       </c>
-      <c r="E155" s="6" t="n">
+      <c r="E155" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="F155" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H155" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="F155" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H155" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I155" s="13" t="n"/>
+      <c r="J155" s="18" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n"/>
-      <c r="B156" s="5" t="n"/>
-      <c r="C156" s="5" t="inlineStr">
+      <c r="A156" s="13" t="n"/>
+      <c r="B156" s="13" t="n"/>
+      <c r="C156" s="13" t="inlineStr">
         <is>
           <t>Die</t>
         </is>
       </c>
-      <c r="D156" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H156" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D156" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H156" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I156" s="13" t="n"/>
+      <c r="J156" s="18" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="8" t="n"/>
-      <c r="B157" s="8" t="n"/>
-      <c r="C157" s="8" t="inlineStr">
+      <c r="A157" s="19" t="n"/>
+      <c r="B157" s="19" t="n"/>
+      <c r="C157" s="19" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D157" s="9" t="n">
+      <c r="D157" s="20" t="n">
         <v>2129.03</v>
       </c>
-      <c r="E157" s="9" t="n">
+      <c r="E157" s="20" t="n">
         <v>350.03</v>
       </c>
-      <c r="F157" s="9" t="n">
+      <c r="F157" s="20" t="n">
         <v>312.34</v>
       </c>
-      <c r="G157" s="10" t="inlineStr">
+      <c r="G157" s="21" t="inlineStr">
         <is>
           <t>+582%</t>
         </is>
       </c>
-      <c r="H157" s="10" t="inlineStr">
+      <c r="H157" s="21" t="inlineStr">
         <is>
           <t>+12%</t>
         </is>
       </c>
-      <c r="I157" s="11" t="n"/>
+      <c r="I157" s="21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J157" s="22" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
+      <c r="I158" s="5" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -4917,6 +5348,8 @@
           <t>+15%</t>
         </is>
       </c>
+      <c r="I159" s="7" t="inlineStr"/>
+      <c r="J159" s="8" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n"/>
@@ -4945,6 +5378,7 @@
           <t>+199%</t>
         </is>
       </c>
+      <c r="I160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n"/>
@@ -4973,6 +5407,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n"/>
@@ -5001,6 +5436,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n"/>
@@ -5029,39 +5465,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I163" s="5" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="8" t="n"/>
-      <c r="B164" s="8" t="n"/>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="A164" s="9" t="n"/>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D164" s="9" t="n">
+      <c r="D164" s="10" t="n">
         <v>982.22</v>
       </c>
-      <c r="E164" s="9" t="n">
+      <c r="E164" s="10" t="n">
         <v>1518.46</v>
       </c>
-      <c r="F164" s="9" t="n">
+      <c r="F164" s="10" t="n">
         <v>231.82</v>
       </c>
-      <c r="G164" s="10" t="inlineStr">
+      <c r="G164" s="11" t="inlineStr">
         <is>
           <t>+324%</t>
         </is>
       </c>
-      <c r="H164" s="10" t="inlineStr">
+      <c r="H164" s="11" t="inlineStr">
         <is>
           <t>+555%</t>
         </is>
       </c>
-      <c r="I164" s="11" t="n"/>
+      <c r="I164" s="9" t="n"/>
+      <c r="J164" s="12" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
+      <c r="I165" s="5" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
@@ -5096,6 +5535,8 @@
           <t>-3%</t>
         </is>
       </c>
+      <c r="I166" s="7" t="inlineStr"/>
+      <c r="J166" s="8" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n"/>
@@ -5124,6 +5565,7 @@
           <t>-3%</t>
         </is>
       </c>
+      <c r="I167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>
@@ -5152,6 +5594,7 @@
           <t>-21%</t>
         </is>
       </c>
+      <c r="I168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n"/>
@@ -5180,6 +5623,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
@@ -5208,39 +5652,42 @@
           <t>-100%</t>
         </is>
       </c>
+      <c r="I170" s="5" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="8" t="n"/>
-      <c r="B171" s="8" t="n"/>
-      <c r="C171" s="8" t="inlineStr">
+      <c r="A171" s="9" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D171" s="9" t="n">
+      <c r="D171" s="10" t="n">
         <v>1072.58</v>
       </c>
-      <c r="E171" s="9" t="n">
+      <c r="E171" s="10" t="n">
         <v>1002.41</v>
       </c>
-      <c r="F171" s="9" t="n">
+      <c r="F171" s="10" t="n">
         <v>1071.74</v>
       </c>
-      <c r="G171" s="10" t="inlineStr">
+      <c r="G171" s="11" t="inlineStr">
         <is>
           <t>+0%</t>
         </is>
       </c>
-      <c r="H171" s="10" t="inlineStr">
+      <c r="H171" s="11" t="inlineStr">
         <is>
           <t>-6%</t>
         </is>
       </c>
-      <c r="I171" s="11" t="n"/>
+      <c r="I171" s="9" t="n"/>
+      <c r="J171" s="12" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
+      <c r="I172" s="5" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="n">
@@ -5275,6 +5722,8 @@
           <t>+118%</t>
         </is>
       </c>
+      <c r="I173" s="7" t="inlineStr"/>
+      <c r="J173" s="8" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n"/>
@@ -5303,6 +5752,7 @@
           <t>-55%</t>
         </is>
       </c>
+      <c r="I174" s="5" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n"/>
@@ -5331,6 +5781,7 @@
           <t>-12%</t>
         </is>
       </c>
+      <c r="I175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n"/>
@@ -5359,6 +5810,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I176" s="5" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n"/>
@@ -5387,39 +5839,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I177" s="5" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="8" t="n"/>
-      <c r="B178" s="8" t="n"/>
-      <c r="C178" s="8" t="inlineStr">
+      <c r="A178" s="9" t="n"/>
+      <c r="B178" s="9" t="n"/>
+      <c r="C178" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D178" s="9" t="n">
+      <c r="D178" s="10" t="n">
         <v>154.32</v>
       </c>
-      <c r="E178" s="9" t="n">
+      <c r="E178" s="10" t="n">
         <v>122.68</v>
       </c>
-      <c r="F178" s="9" t="n">
+      <c r="F178" s="10" t="n">
         <v>193.79</v>
       </c>
-      <c r="G178" s="10" t="inlineStr">
+      <c r="G178" s="11" t="inlineStr">
         <is>
           <t>-20%</t>
         </is>
       </c>
-      <c r="H178" s="10" t="inlineStr">
+      <c r="H178" s="11" t="inlineStr">
         <is>
           <t>-37%</t>
         </is>
       </c>
-      <c r="I178" s="11" t="n"/>
+      <c r="I178" s="9" t="n"/>
+      <c r="J178" s="12" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
+      <c r="I179" s="5" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="n">
@@ -5454,6 +5909,8 @@
           <t>+7%</t>
         </is>
       </c>
+      <c r="I180" s="7" t="inlineStr"/>
+      <c r="J180" s="8" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n"/>
@@ -5482,6 +5939,7 @@
           <t>+19%</t>
         </is>
       </c>
+      <c r="I181" s="5" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n"/>
@@ -5510,6 +5968,7 @@
           <t>-84%</t>
         </is>
       </c>
+      <c r="I182" s="5" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n"/>
@@ -5538,6 +5997,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I183" s="5" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n"/>
@@ -5566,39 +6026,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I184" s="5" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="8" t="n"/>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="8" t="inlineStr">
+      <c r="A185" s="9" t="n"/>
+      <c r="B185" s="9" t="n"/>
+      <c r="C185" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D185" s="9" t="n">
+      <c r="D185" s="10" t="n">
         <v>3305.91</v>
       </c>
-      <c r="E185" s="9" t="n">
+      <c r="E185" s="10" t="n">
         <v>1970.05</v>
       </c>
-      <c r="F185" s="9" t="n">
+      <c r="F185" s="10" t="n">
         <v>3003.75</v>
       </c>
-      <c r="G185" s="10" t="inlineStr">
+      <c r="G185" s="11" t="inlineStr">
         <is>
           <t>+10%</t>
         </is>
       </c>
-      <c r="H185" s="10" t="inlineStr">
+      <c r="H185" s="11" t="inlineStr">
         <is>
           <t>-34%</t>
         </is>
       </c>
-      <c r="I185" s="11" t="n"/>
+      <c r="I185" s="9" t="n"/>
+      <c r="J185" s="12" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
+      <c r="I186" s="5" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -5633,6 +6096,8 @@
           <t>-5%</t>
         </is>
       </c>
+      <c r="I187" s="7" t="inlineStr"/>
+      <c r="J187" s="8" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n"/>
@@ -5661,6 +6126,7 @@
           <t>-43%</t>
         </is>
       </c>
+      <c r="I188" s="5" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n"/>
@@ -5689,6 +6155,7 @@
           <t>-49%</t>
         </is>
       </c>
+      <c r="I189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n"/>
@@ -5717,6 +6184,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I190" s="5" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n"/>
@@ -5745,39 +6213,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I191" s="5" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="8" t="n"/>
-      <c r="B192" s="8" t="n"/>
-      <c r="C192" s="8" t="inlineStr">
+      <c r="A192" s="9" t="n"/>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D192" s="9" t="n">
+      <c r="D192" s="10" t="n">
         <v>986.5599999999999</v>
       </c>
-      <c r="E192" s="9" t="n">
+      <c r="E192" s="10" t="n">
         <v>940.65</v>
       </c>
-      <c r="F192" s="9" t="n">
+      <c r="F192" s="10" t="n">
         <v>1538.49</v>
       </c>
-      <c r="G192" s="10" t="inlineStr">
+      <c r="G192" s="11" t="inlineStr">
         <is>
           <t>-36%</t>
         </is>
       </c>
-      <c r="H192" s="10" t="inlineStr">
+      <c r="H192" s="11" t="inlineStr">
         <is>
           <t>-39%</t>
         </is>
       </c>
-      <c r="I192" s="11" t="n"/>
+      <c r="I192" s="9" t="n"/>
+      <c r="J192" s="12" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
+      <c r="I193" s="5" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="n">
@@ -5788,180 +6259,199 @@
           <t>RW-260804-155659 / 223327</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
+      <c r="C194" s="13" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D194" s="6" t="n">
+      <c r="D194" s="14" t="n">
         <v>96.91</v>
       </c>
-      <c r="E194" s="6" t="n">
+      <c r="E194" s="14" t="n">
         <v>103.17</v>
       </c>
-      <c r="F194" s="6" t="n">
+      <c r="F194" s="14" t="n">
         <v>97.95999999999999</v>
       </c>
-      <c r="G194" s="7" t="inlineStr">
+      <c r="G194" s="15" t="inlineStr">
         <is>
           <t>-1%</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr">
+      <c r="H194" s="15" t="inlineStr">
         <is>
           <t>+5%</t>
         </is>
       </c>
-      <c r="I194" s="12" t="inlineStr">
+      <c r="I194" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J194" s="17" t="inlineStr">
         <is>
           <t>[Actual] This job was supposed to just be a cut/ship on the zund.  Could not find any actual data for the zund for setup/run; invoiced for iquote amt.</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="n"/>
-      <c r="B195" s="5" t="n"/>
-      <c r="C195" s="5" t="inlineStr">
+      <c r="A195" s="13" t="n"/>
+      <c r="B195" s="13" t="n"/>
+      <c r="C195" s="13" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="D195" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E195" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F195" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H195" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D195" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H195" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I195" s="13" t="n"/>
+      <c r="J195" s="18" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="n"/>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="5" t="inlineStr">
+      <c r="A196" s="13" t="n"/>
+      <c r="B196" s="13" t="n"/>
+      <c r="C196" s="13" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="D196" s="6" t="n">
+      <c r="D196" s="14" t="n">
         <v>352.12</v>
       </c>
-      <c r="E196" s="6" t="n">
+      <c r="E196" s="14" t="n">
         <v>825.6</v>
       </c>
-      <c r="F196" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="F196" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H196" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I196" s="13" t="n"/>
+      <c r="J196" s="18" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="n"/>
-      <c r="B197" s="5" t="n"/>
-      <c r="C197" s="5" t="inlineStr">
+      <c r="A197" s="13" t="n"/>
+      <c r="B197" s="13" t="n"/>
+      <c r="C197" s="13" t="inlineStr">
         <is>
           <t>Handwork</t>
         </is>
       </c>
-      <c r="D197" s="6" t="n">
+      <c r="D197" s="14" t="n">
         <v>19.83</v>
       </c>
-      <c r="E197" s="6" t="n">
+      <c r="E197" s="14" t="n">
         <v>86.17</v>
       </c>
-      <c r="F197" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H197" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="F197" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H197" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I197" s="13" t="n"/>
+      <c r="J197" s="18" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="n"/>
-      <c r="B198" s="5" t="n"/>
-      <c r="C198" s="5" t="inlineStr">
+      <c r="A198" s="13" t="n"/>
+      <c r="B198" s="13" t="n"/>
+      <c r="C198" s="13" t="inlineStr">
         <is>
           <t>Die</t>
         </is>
       </c>
-      <c r="D198" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E198" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F198" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D198" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H198" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I198" s="13" t="n"/>
+      <c r="J198" s="18" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="8" t="n"/>
-      <c r="B199" s="8" t="n"/>
-      <c r="C199" s="8" t="inlineStr">
+      <c r="A199" s="19" t="n"/>
+      <c r="B199" s="19" t="n"/>
+      <c r="C199" s="19" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D199" s="9" t="n">
+      <c r="D199" s="20" t="n">
         <v>468.86</v>
       </c>
-      <c r="E199" s="9" t="n">
+      <c r="E199" s="20" t="n">
         <v>1014.94</v>
       </c>
-      <c r="F199" s="9" t="n">
+      <c r="F199" s="20" t="n">
         <v>97.95999999999999</v>
       </c>
-      <c r="G199" s="10" t="inlineStr">
+      <c r="G199" s="21" t="inlineStr">
         <is>
           <t>+379%</t>
         </is>
       </c>
-      <c r="H199" s="10" t="inlineStr">
+      <c r="H199" s="21" t="inlineStr">
         <is>
           <t>+936%</t>
         </is>
       </c>
-      <c r="I199" s="11" t="n"/>
+      <c r="I199" s="21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J199" s="22" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
+      <c r="I200" s="5" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
@@ -5996,6 +6486,8 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I201" s="7" t="inlineStr"/>
+      <c r="J201" s="8" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n"/>
@@ -6024,6 +6516,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I202" s="5" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n"/>
@@ -6052,6 +6545,7 @@
           <t>+17%</t>
         </is>
       </c>
+      <c r="I203" s="5" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n"/>
@@ -6080,6 +6574,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I204" s="5" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n"/>
@@ -6108,39 +6603,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I205" s="5" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="8" t="n"/>
-      <c r="B206" s="8" t="n"/>
-      <c r="C206" s="8" t="inlineStr">
+      <c r="A206" s="9" t="n"/>
+      <c r="B206" s="9" t="n"/>
+      <c r="C206" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D206" s="9" t="n">
+      <c r="D206" s="10" t="n">
         <v>1298.55</v>
       </c>
-      <c r="E206" s="9" t="n">
+      <c r="E206" s="10" t="n">
         <v>1052.45</v>
       </c>
-      <c r="F206" s="9" t="n">
+      <c r="F206" s="10" t="n">
         <v>347.88</v>
       </c>
-      <c r="G206" s="10" t="inlineStr">
+      <c r="G206" s="11" t="inlineStr">
         <is>
           <t>+273%</t>
         </is>
       </c>
-      <c r="H206" s="10" t="inlineStr">
+      <c r="H206" s="11" t="inlineStr">
         <is>
           <t>+203%</t>
         </is>
       </c>
-      <c r="I206" s="11" t="n"/>
+      <c r="I206" s="9" t="n"/>
+      <c r="J206" s="12" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
+      <c r="I207" s="5" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
@@ -6175,6 +6673,8 @@
           <t>-30%</t>
         </is>
       </c>
+      <c r="I208" s="7" t="inlineStr"/>
+      <c r="J208" s="8" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n"/>
@@ -6203,6 +6703,7 @@
           <t>-49%</t>
         </is>
       </c>
+      <c r="I209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n"/>
@@ -6231,6 +6732,7 @@
           <t>-49%</t>
         </is>
       </c>
+      <c r="I210" s="5" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n"/>
@@ -6259,6 +6761,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I211" s="5" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n"/>
@@ -6287,39 +6790,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I212" s="5" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="8" t="n"/>
-      <c r="B213" s="8" t="n"/>
-      <c r="C213" s="8" t="inlineStr">
+      <c r="A213" s="9" t="n"/>
+      <c r="B213" s="9" t="n"/>
+      <c r="C213" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D213" s="9" t="n">
+      <c r="D213" s="10" t="n">
         <v>338.33</v>
       </c>
-      <c r="E213" s="9" t="n">
+      <c r="E213" s="10" t="n">
         <v>347.17</v>
       </c>
-      <c r="F213" s="9" t="n">
+      <c r="F213" s="10" t="n">
         <v>632.61</v>
       </c>
-      <c r="G213" s="10" t="inlineStr">
+      <c r="G213" s="11" t="inlineStr">
         <is>
           <t>-47%</t>
         </is>
       </c>
-      <c r="H213" s="10" t="inlineStr">
+      <c r="H213" s="11" t="inlineStr">
         <is>
           <t>-45%</t>
         </is>
       </c>
-      <c r="I213" s="11" t="n"/>
+      <c r="I213" s="9" t="n"/>
+      <c r="J213" s="12" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
+      <c r="I214" s="5" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
@@ -6354,6 +6860,8 @@
           <t>-36%</t>
         </is>
       </c>
+      <c r="I215" s="7" t="inlineStr"/>
+      <c r="J215" s="8" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n"/>
@@ -6382,6 +6890,7 @@
           <t>-64%</t>
         </is>
       </c>
+      <c r="I216" s="5" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n"/>
@@ -6410,6 +6919,7 @@
           <t>-58%</t>
         </is>
       </c>
+      <c r="I217" s="5" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n"/>
@@ -6438,6 +6948,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I218" s="5" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n"/>
@@ -6466,39 +6977,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I219" s="5" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="8" t="n"/>
-      <c r="B220" s="8" t="n"/>
-      <c r="C220" s="8" t="inlineStr">
+      <c r="A220" s="9" t="n"/>
+      <c r="B220" s="9" t="n"/>
+      <c r="C220" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D220" s="9" t="n">
+      <c r="D220" s="10" t="n">
         <v>898.4299999999999</v>
       </c>
-      <c r="E220" s="9" t="n">
+      <c r="E220" s="10" t="n">
         <v>732.17</v>
       </c>
-      <c r="F220" s="9" t="n">
+      <c r="F220" s="10" t="n">
         <v>1630.91</v>
       </c>
-      <c r="G220" s="10" t="inlineStr">
+      <c r="G220" s="11" t="inlineStr">
         <is>
           <t>-45%</t>
         </is>
       </c>
-      <c r="H220" s="10" t="inlineStr">
+      <c r="H220" s="11" t="inlineStr">
         <is>
           <t>-55%</t>
         </is>
       </c>
-      <c r="I220" s="11" t="n"/>
+      <c r="I220" s="9" t="n"/>
+      <c r="J220" s="12" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
+      <c r="I221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="n">
@@ -6533,6 +7047,8 @@
           <t>+43%</t>
         </is>
       </c>
+      <c r="I222" s="7" t="inlineStr"/>
+      <c r="J222" s="8" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n"/>
@@ -6561,6 +7077,7 @@
           <t>-29%</t>
         </is>
       </c>
+      <c r="I223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n"/>
@@ -6589,6 +7106,7 @@
           <t>-52%</t>
         </is>
       </c>
+      <c r="I224" s="5" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n"/>
@@ -6617,6 +7135,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I225" s="5" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n"/>
@@ -6645,39 +7164,42 @@
           <t>-100%</t>
         </is>
       </c>
+      <c r="I226" s="5" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="8" t="n"/>
-      <c r="B227" s="8" t="n"/>
-      <c r="C227" s="8" t="inlineStr">
+      <c r="A227" s="9" t="n"/>
+      <c r="B227" s="9" t="n"/>
+      <c r="C227" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D227" s="9" t="n">
+      <c r="D227" s="10" t="n">
         <v>4278.3</v>
       </c>
-      <c r="E227" s="9" t="n">
+      <c r="E227" s="10" t="n">
         <v>3146.43</v>
       </c>
-      <c r="F227" s="9" t="n">
+      <c r="F227" s="10" t="n">
         <v>3565.9</v>
       </c>
-      <c r="G227" s="10" t="inlineStr">
+      <c r="G227" s="11" t="inlineStr">
         <is>
           <t>+20%</t>
         </is>
       </c>
-      <c r="H227" s="10" t="inlineStr">
+      <c r="H227" s="11" t="inlineStr">
         <is>
           <t>-12%</t>
         </is>
       </c>
-      <c r="I227" s="11" t="n"/>
+      <c r="I227" s="9" t="n"/>
+      <c r="J227" s="12" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
+      <c r="I228" s="5" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="n">
@@ -6712,6 +7234,8 @@
           <t>-38%</t>
         </is>
       </c>
+      <c r="I229" s="7" t="inlineStr"/>
+      <c r="J229" s="8" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n"/>
@@ -6740,6 +7264,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I230" s="5" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n"/>
@@ -6768,6 +7293,7 @@
           <t>-47%</t>
         </is>
       </c>
+      <c r="I231" s="5" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n"/>
@@ -6796,6 +7322,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n"/>
@@ -6824,39 +7351,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I233" s="5" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="8" t="n"/>
-      <c r="B234" s="8" t="n"/>
-      <c r="C234" s="8" t="inlineStr">
+      <c r="A234" s="9" t="n"/>
+      <c r="B234" s="9" t="n"/>
+      <c r="C234" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D234" s="9" t="n">
+      <c r="D234" s="10" t="n">
         <v>127.81</v>
       </c>
-      <c r="E234" s="9" t="n">
+      <c r="E234" s="10" t="n">
         <v>114.16</v>
       </c>
-      <c r="F234" s="9" t="n">
+      <c r="F234" s="10" t="n">
         <v>206.83</v>
       </c>
-      <c r="G234" s="10" t="inlineStr">
+      <c r="G234" s="11" t="inlineStr">
         <is>
           <t>-38%</t>
         </is>
       </c>
-      <c r="H234" s="10" t="inlineStr">
+      <c r="H234" s="11" t="inlineStr">
         <is>
           <t>-45%</t>
         </is>
       </c>
-      <c r="I234" s="11" t="n"/>
+      <c r="I234" s="9" t="n"/>
+      <c r="J234" s="12" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
+      <c r="I235" s="5" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="n">
@@ -6891,6 +7421,8 @@
           <t>+12%</t>
         </is>
       </c>
+      <c r="I236" s="7" t="inlineStr"/>
+      <c r="J236" s="8" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n"/>
@@ -6919,6 +7451,7 @@
           <t>-80%</t>
         </is>
       </c>
+      <c r="I237" s="5" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n"/>
@@ -6947,6 +7480,7 @@
           <t>+37%</t>
         </is>
       </c>
+      <c r="I238" s="5" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n"/>
@@ -6975,6 +7509,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I239" s="5" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n"/>
@@ -7003,39 +7538,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I240" s="5" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="8" t="n"/>
-      <c r="B241" s="8" t="n"/>
-      <c r="C241" s="8" t="inlineStr">
+      <c r="A241" s="9" t="n"/>
+      <c r="B241" s="9" t="n"/>
+      <c r="C241" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D241" s="9" t="n">
+      <c r="D241" s="10" t="n">
         <v>557.2</v>
       </c>
-      <c r="E241" s="9" t="n">
+      <c r="E241" s="10" t="n">
         <v>487.62</v>
       </c>
-      <c r="F241" s="9" t="n">
+      <c r="F241" s="10" t="n">
         <v>926.42</v>
       </c>
-      <c r="G241" s="10" t="inlineStr">
+      <c r="G241" s="11" t="inlineStr">
         <is>
           <t>-40%</t>
         </is>
       </c>
-      <c r="H241" s="10" t="inlineStr">
+      <c r="H241" s="11" t="inlineStr">
         <is>
           <t>-47%</t>
         </is>
       </c>
-      <c r="I241" s="11" t="n"/>
+      <c r="I241" s="9" t="n"/>
+      <c r="J241" s="12" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
+      <c r="I242" s="5" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n">
@@ -7070,6 +7608,8 @@
           <t>-62%</t>
         </is>
       </c>
+      <c r="I243" s="7" t="inlineStr"/>
+      <c r="J243" s="8" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n"/>
@@ -7098,6 +7638,7 @@
           <t>-52%</t>
         </is>
       </c>
+      <c r="I244" s="5" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n"/>
@@ -7126,6 +7667,7 @@
           <t>-18%</t>
         </is>
       </c>
+      <c r="I245" s="5" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n"/>
@@ -7154,6 +7696,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I246" s="5" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n"/>
@@ -7182,39 +7725,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I247" s="5" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="8" t="n"/>
-      <c r="B248" s="8" t="n"/>
-      <c r="C248" s="8" t="inlineStr">
+      <c r="A248" s="9" t="n"/>
+      <c r="B248" s="9" t="n"/>
+      <c r="C248" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D248" s="9" t="n">
+      <c r="D248" s="10" t="n">
         <v>500.37</v>
       </c>
-      <c r="E248" s="9" t="n">
+      <c r="E248" s="10" t="n">
         <v>452.99</v>
       </c>
-      <c r="F248" s="9" t="n">
+      <c r="F248" s="10" t="n">
         <v>820.77</v>
       </c>
-      <c r="G248" s="10" t="inlineStr">
+      <c r="G248" s="11" t="inlineStr">
         <is>
           <t>-39%</t>
         </is>
       </c>
-      <c r="H248" s="10" t="inlineStr">
+      <c r="H248" s="11" t="inlineStr">
         <is>
           <t>-45%</t>
         </is>
       </c>
-      <c r="I248" s="11" t="n"/>
+      <c r="I248" s="9" t="n"/>
+      <c r="J248" s="12" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
+      <c r="I249" s="5" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="n">
@@ -7225,180 +7771,199 @@
           <t>RW-260722-082345 / 223591</t>
         </is>
       </c>
-      <c r="C250" s="5" t="inlineStr">
+      <c r="C250" s="13" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D250" s="6" t="n">
+      <c r="D250" s="14" t="n">
         <v>1841.01</v>
       </c>
-      <c r="E250" s="6" t="n">
+      <c r="E250" s="14" t="n">
         <v>794.2</v>
       </c>
-      <c r="F250" s="6" t="n">
+      <c r="F250" s="14" t="n">
         <v>2272.71</v>
       </c>
-      <c r="G250" s="7" t="inlineStr">
+      <c r="G250" s="15" t="inlineStr">
         <is>
           <t>-19%</t>
         </is>
       </c>
-      <c r="H250" s="7" t="inlineStr">
+      <c r="H250" s="15" t="inlineStr">
         <is>
           <t>-65%</t>
         </is>
       </c>
-      <c r="I250" s="12" t="inlineStr">
+      <c r="I250" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J250" s="17" t="inlineStr">
         <is>
           <t>[iQuote] actual was cut on kongsburg</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="n"/>
-      <c r="B251" s="5" t="n"/>
-      <c r="C251" s="5" t="inlineStr">
+      <c r="A251" s="13" t="n"/>
+      <c r="B251" s="13" t="n"/>
+      <c r="C251" s="13" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="D251" s="6" t="n">
+      <c r="D251" s="14" t="n">
         <v>2331.33</v>
       </c>
-      <c r="E251" s="6" t="n">
+      <c r="E251" s="14" t="n">
         <v>801.39</v>
       </c>
-      <c r="F251" s="6" t="n">
+      <c r="F251" s="14" t="n">
         <v>4041.83</v>
       </c>
-      <c r="G251" s="7" t="inlineStr">
+      <c r="G251" s="15" t="inlineStr">
         <is>
           <t>-42%</t>
         </is>
       </c>
-      <c r="H251" s="7" t="inlineStr">
+      <c r="H251" s="15" t="inlineStr">
         <is>
           <t>-80%</t>
         </is>
       </c>
+      <c r="I251" s="13" t="n"/>
+      <c r="J251" s="18" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="5" t="n"/>
-      <c r="B252" s="5" t="n"/>
-      <c r="C252" s="5" t="inlineStr">
+      <c r="A252" s="13" t="n"/>
+      <c r="B252" s="13" t="n"/>
+      <c r="C252" s="13" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="D252" s="6" t="n">
+      <c r="D252" s="14" t="n">
         <v>461.58</v>
       </c>
-      <c r="E252" s="6" t="n">
+      <c r="E252" s="14" t="n">
         <v>645.5</v>
       </c>
-      <c r="F252" s="6" t="n">
+      <c r="F252" s="14" t="n">
         <v>1304.72</v>
       </c>
-      <c r="G252" s="7" t="inlineStr">
+      <c r="G252" s="15" t="inlineStr">
         <is>
           <t>-65%</t>
         </is>
       </c>
-      <c r="H252" s="7" t="inlineStr">
+      <c r="H252" s="15" t="inlineStr">
         <is>
           <t>-51%</t>
         </is>
       </c>
+      <c r="I252" s="13" t="n"/>
+      <c r="J252" s="18" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="n"/>
-      <c r="B253" s="5" t="n"/>
-      <c r="C253" s="5" t="inlineStr">
+      <c r="A253" s="13" t="n"/>
+      <c r="B253" s="13" t="n"/>
+      <c r="C253" s="13" t="inlineStr">
         <is>
           <t>Handwork</t>
         </is>
       </c>
-      <c r="D253" s="6" t="n">
+      <c r="D253" s="14" t="n">
         <v>356.25</v>
       </c>
-      <c r="E253" s="6" t="n">
+      <c r="E253" s="14" t="n">
         <v>135</v>
       </c>
-      <c r="F253" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H253" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="F253" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H253" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I253" s="13" t="n"/>
+      <c r="J253" s="18" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="n"/>
-      <c r="B254" s="5" t="n"/>
-      <c r="C254" s="5" t="inlineStr">
+      <c r="A254" s="13" t="n"/>
+      <c r="B254" s="13" t="n"/>
+      <c r="C254" s="13" t="inlineStr">
         <is>
           <t>Die</t>
         </is>
       </c>
-      <c r="D254" s="6" t="n">
+      <c r="D254" s="14" t="n">
         <v>1380</v>
       </c>
-      <c r="E254" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F254" s="6" t="n">
+      <c r="E254" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="14" t="n">
         <v>916</v>
       </c>
-      <c r="G254" s="7" t="inlineStr">
+      <c r="G254" s="15" t="inlineStr">
         <is>
           <t>+51%</t>
         </is>
       </c>
-      <c r="H254" s="7" t="inlineStr">
+      <c r="H254" s="15" t="inlineStr">
         <is>
           <t>-100%</t>
         </is>
       </c>
+      <c r="I254" s="13" t="n"/>
+      <c r="J254" s="18" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="8" t="n"/>
-      <c r="B255" s="8" t="n"/>
-      <c r="C255" s="8" t="inlineStr">
+      <c r="A255" s="19" t="n"/>
+      <c r="B255" s="19" t="n"/>
+      <c r="C255" s="19" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D255" s="9" t="n">
+      <c r="D255" s="20" t="n">
         <v>4990.17</v>
       </c>
-      <c r="E255" s="9" t="n">
+      <c r="E255" s="20" t="n">
         <v>2376.09</v>
       </c>
-      <c r="F255" s="9" t="n">
+      <c r="F255" s="20" t="n">
         <v>7619.26</v>
       </c>
-      <c r="G255" s="10" t="inlineStr">
+      <c r="G255" s="21" t="inlineStr">
         <is>
           <t>-35%</t>
         </is>
       </c>
-      <c r="H255" s="10" t="inlineStr">
+      <c r="H255" s="21" t="inlineStr">
         <is>
           <t>-69%</t>
         </is>
       </c>
-      <c r="I255" s="11" t="n"/>
+      <c r="I255" s="21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J255" s="22" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
+      <c r="I256" s="5" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
@@ -7433,6 +7998,8 @@
           <t>-4%</t>
         </is>
       </c>
+      <c r="I257" s="7" t="inlineStr"/>
+      <c r="J257" s="8" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="5" t="n"/>
@@ -7461,6 +8028,7 @@
           <t>-59%</t>
         </is>
       </c>
+      <c r="I258" s="5" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="5" t="n"/>
@@ -7489,6 +8057,7 @@
           <t>-45%</t>
         </is>
       </c>
+      <c r="I259" s="5" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n"/>
@@ -7517,6 +8086,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I260" s="5" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n"/>
@@ -7545,39 +8115,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I261" s="5" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="8" t="n"/>
-      <c r="B262" s="8" t="n"/>
-      <c r="C262" s="8" t="inlineStr">
+      <c r="A262" s="9" t="n"/>
+      <c r="B262" s="9" t="n"/>
+      <c r="C262" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D262" s="9" t="n">
+      <c r="D262" s="10" t="n">
         <v>1989.98</v>
       </c>
-      <c r="E262" s="9" t="n">
+      <c r="E262" s="10" t="n">
         <v>1543.98</v>
       </c>
-      <c r="F262" s="9" t="n">
+      <c r="F262" s="10" t="n">
         <v>2580</v>
       </c>
-      <c r="G262" s="10" t="inlineStr">
+      <c r="G262" s="11" t="inlineStr">
         <is>
           <t>-23%</t>
         </is>
       </c>
-      <c r="H262" s="10" t="inlineStr">
+      <c r="H262" s="11" t="inlineStr">
         <is>
           <t>-40%</t>
         </is>
       </c>
-      <c r="I262" s="11" t="n"/>
+      <c r="I262" s="9" t="n"/>
+      <c r="J262" s="12" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
+      <c r="I263" s="5" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="n">
@@ -7612,6 +8185,8 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I264" s="7" t="inlineStr"/>
+      <c r="J264" s="8" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="5" t="n"/>
@@ -7640,6 +8215,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I265" s="5" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="5" t="n"/>
@@ -7668,6 +8244,7 @@
           <t>-75%</t>
         </is>
       </c>
+      <c r="I266" s="5" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="5" t="n"/>
@@ -7696,6 +8273,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I267" s="5" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="5" t="n"/>
@@ -7724,39 +8302,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I268" s="5" t="n"/>
     </row>
     <row r="269">
-      <c r="A269" s="8" t="n"/>
-      <c r="B269" s="8" t="n"/>
-      <c r="C269" s="8" t="inlineStr">
+      <c r="A269" s="9" t="n"/>
+      <c r="B269" s="9" t="n"/>
+      <c r="C269" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D269" s="9" t="n">
+      <c r="D269" s="10" t="n">
         <v>66.2</v>
       </c>
-      <c r="E269" s="9" t="n">
+      <c r="E269" s="10" t="n">
         <v>52.35</v>
       </c>
-      <c r="F269" s="9" t="n">
+      <c r="F269" s="10" t="n">
         <v>163.97</v>
       </c>
-      <c r="G269" s="10" t="inlineStr">
+      <c r="G269" s="11" t="inlineStr">
         <is>
           <t>-60%</t>
         </is>
       </c>
-      <c r="H269" s="10" t="inlineStr">
+      <c r="H269" s="11" t="inlineStr">
         <is>
           <t>-68%</t>
         </is>
       </c>
-      <c r="I269" s="11" t="n"/>
+      <c r="I269" s="9" t="n"/>
+      <c r="J269" s="12" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
+      <c r="I270" s="5" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n">
@@ -7791,6 +8372,8 @@
           <t>+15%</t>
         </is>
       </c>
+      <c r="I271" s="7" t="inlineStr"/>
+      <c r="J271" s="8" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n"/>
@@ -7819,6 +8402,7 @@
           <t>-53%</t>
         </is>
       </c>
+      <c r="I272" s="5" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="5" t="n"/>
@@ -7847,6 +8431,7 @@
           <t>+43%</t>
         </is>
       </c>
+      <c r="I273" s="5" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="5" t="n"/>
@@ -7875,6 +8460,7 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I274" s="5" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="5" t="n"/>
@@ -7903,39 +8489,42 @@
           <t>n/a</t>
         </is>
       </c>
+      <c r="I275" s="5" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="8" t="n"/>
-      <c r="B276" s="8" t="n"/>
-      <c r="C276" s="8" t="inlineStr">
+      <c r="A276" s="9" t="n"/>
+      <c r="B276" s="9" t="n"/>
+      <c r="C276" s="9" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D276" s="9" t="n">
+      <c r="D276" s="10" t="n">
         <v>518.8099999999999</v>
       </c>
-      <c r="E276" s="9" t="n">
+      <c r="E276" s="10" t="n">
         <v>575.1900000000001</v>
       </c>
-      <c r="F276" s="9" t="n">
+      <c r="F276" s="10" t="n">
         <v>653.51</v>
       </c>
-      <c r="G276" s="10" t="inlineStr">
+      <c r="G276" s="11" t="inlineStr">
         <is>
           <t>-21%</t>
         </is>
       </c>
-      <c r="H276" s="10" t="inlineStr">
+      <c r="H276" s="11" t="inlineStr">
         <is>
           <t>-12%</t>
         </is>
       </c>
-      <c r="I276" s="11" t="n"/>
+      <c r="I276" s="9" t="n"/>
+      <c r="J276" s="12" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
+      <c r="I277" s="5" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="4" t="n">
@@ -7946,185 +8535,266 @@
           <t>RW-260803-100141 / 223880</t>
         </is>
       </c>
-      <c r="C278" s="5" t="inlineStr">
+      <c r="C278" s="13" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="D278" s="6" t="n">
+      <c r="D278" s="14" t="n">
         <v>300.33</v>
       </c>
-      <c r="E278" s="6" t="n">
+      <c r="E278" s="14" t="n">
         <v>430.7</v>
       </c>
-      <c r="F278" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H278" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I278" s="12" t="inlineStr">
+      <c r="F278" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H278" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I278" s="16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J278" s="17" t="inlineStr">
         <is>
           <t>[iQuote] Pre-invoiced only, ran 8/10, estimated hrs on zund was 14.51, plan was 20.73, SPOT gave 12.8 actual was 1.228; material costs missing? Plan said:  511Q051KR63002 but not charged to job in material transaction tables?; [Actual] I do not have material cost data for this record - allegedly ran 8/10</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="5" t="n"/>
-      <c r="B279" s="5" t="n"/>
-      <c r="C279" s="5" t="inlineStr">
+      <c r="A279" s="13" t="n"/>
+      <c r="B279" s="13" t="n"/>
+      <c r="C279" s="13" t="inlineStr">
         <is>
           <t>Print</t>
         </is>
       </c>
-      <c r="D279" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E279" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F279" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H279" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D279" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H279" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I279" s="13" t="n"/>
+      <c r="J279" s="18" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="5" t="n"/>
-      <c r="B280" s="5" t="n"/>
-      <c r="C280" s="5" t="inlineStr">
+      <c r="A280" s="13" t="n"/>
+      <c r="B280" s="13" t="n"/>
+      <c r="C280" s="13" t="inlineStr">
         <is>
           <t>Cutting</t>
         </is>
       </c>
-      <c r="D280" s="6" t="n">
+      <c r="D280" s="14" t="n">
         <v>1760.55</v>
       </c>
-      <c r="E280" s="6" t="n">
+      <c r="E280" s="14" t="n">
         <v>1035.96</v>
       </c>
-      <c r="F280" s="6" t="n">
+      <c r="F280" s="14" t="n">
         <v>104.36</v>
       </c>
-      <c r="G280" s="7" t="inlineStr">
+      <c r="G280" s="15" t="inlineStr">
         <is>
           <t>+1587%</t>
         </is>
       </c>
-      <c r="H280" s="7" t="inlineStr">
+      <c r="H280" s="15" t="inlineStr">
         <is>
           <t>+893%</t>
         </is>
       </c>
+      <c r="I280" s="13" t="n"/>
+      <c r="J280" s="18" t="n"/>
     </row>
     <row r="281">
-      <c r="A281" s="5" t="n"/>
-      <c r="B281" s="5" t="n"/>
-      <c r="C281" s="5" t="inlineStr">
+      <c r="A281" s="13" t="n"/>
+      <c r="B281" s="13" t="n"/>
+      <c r="C281" s="13" t="inlineStr">
         <is>
           <t>Handwork</t>
         </is>
       </c>
-      <c r="D281" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E281" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F281" s="6" t="n">
+      <c r="D281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F281" s="14" t="n">
         <v>89.27</v>
       </c>
-      <c r="G281" s="7" t="inlineStr">
+      <c r="G281" s="15" t="inlineStr">
         <is>
           <t>-100%</t>
         </is>
       </c>
-      <c r="H281" s="7" t="inlineStr">
+      <c r="H281" s="15" t="inlineStr">
         <is>
           <t>-100%</t>
         </is>
       </c>
+      <c r="I281" s="13" t="n"/>
+      <c r="J281" s="18" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="5" t="n"/>
-      <c r="B282" s="5" t="n"/>
-      <c r="C282" s="5" t="inlineStr">
+      <c r="A282" s="13" t="n"/>
+      <c r="B282" s="13" t="n"/>
+      <c r="C282" s="13" t="inlineStr">
         <is>
           <t>Die</t>
         </is>
       </c>
-      <c r="D282" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E282" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F282" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G282" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H282" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
+      <c r="D282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F282" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H282" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I282" s="13" t="n"/>
+      <c r="J282" s="18" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="8" t="n"/>
-      <c r="B283" s="8" t="n"/>
-      <c r="C283" s="8" t="inlineStr">
+      <c r="A283" s="19" t="n"/>
+      <c r="B283" s="19" t="n"/>
+      <c r="C283" s="19" t="inlineStr">
         <is>
           <t>TOTAL (excl die)</t>
         </is>
       </c>
-      <c r="D283" s="9" t="n">
+      <c r="D283" s="20" t="n">
         <v>2060.88</v>
       </c>
-      <c r="E283" s="9" t="n">
+      <c r="E283" s="20" t="n">
         <v>1466.66</v>
       </c>
-      <c r="F283" s="9" t="n">
+      <c r="F283" s="20" t="n">
         <v>193.63</v>
       </c>
-      <c r="G283" s="10" t="inlineStr">
+      <c r="G283" s="21" t="inlineStr">
         <is>
           <t>+964%</t>
         </is>
       </c>
-      <c r="H283" s="10" t="inlineStr">
+      <c r="H283" s="21" t="inlineStr">
         <is>
           <t>+657%</t>
         </is>
       </c>
-      <c r="I283" s="11" t="n"/>
+      <c r="I283" s="21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J283" s="22" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
+      <c r="I284" s="5" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>OUTLIER LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="30" customHeight="1">
+      <c r="A287" s="22" t="n">
+        <v>236663</v>
+      </c>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>SPOT Buy Min: 663 sheets forced (ECT 32 B 45.25x72) — actual production used different qty; iQuote also has $0 material in DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="30" customHeight="1">
+      <c r="A288" s="22" t="n">
+        <v>236559</v>
+      </c>
+      <c r="B288" s="8" t="inlineStr">
+        <is>
+          <t>SPOT Buy Min: 663 sheets forced (ECT 32 SW C 45.25x72 K/K) — actual production used 55x76 @ 50 sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="30" customHeight="1">
+      <c r="A289" s="22" t="n">
+        <v>236477</v>
+      </c>
+      <c r="B289" s="8" t="inlineStr">
+        <is>
+          <t>Cut/ship only on Zund — no actual Zund setup/run data captured; invoiced at iQuote $</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="30" customHeight="1">
+      <c r="A290" s="22" t="n">
+        <v>236943</v>
+      </c>
+      <c r="B290" s="8" t="inlineStr">
+        <is>
+          <t>Actual was cut on Kongsberg (not the machine SPOT/iQuote planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="30" customHeight="1">
+      <c r="A291" s="22" t="n">
+        <v>237385</v>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
+        <is>
+          <t>Pre-invoiced only; material cost data missing from actual (allegedly ran 8/10)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B287:J287"/>
+    <mergeCell ref="B288:J288"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B290:J290"/>
+    <mergeCell ref="B291:J291"/>
+    <mergeCell ref="B289:J289"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8136,41 +8806,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Price Comparison actual 40 produced jobs</t>
+          <t>Price Comparison — 40 produced jobs (5 outliers flagged, 35 clean)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>MIS Job</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Actual Invoice $</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>iQuote Sell $</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>SPOT Sell $</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Outlier?</t>
         </is>
       </c>
     </row>
@@ -8180,15 +8858,16 @@
           <t>234843</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="24" t="n">
         <v>1216</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="24" t="n">
         <v>1216</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="24" t="n">
         <v>1486</v>
       </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -8196,15 +8875,16 @@
           <t>235366</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="24" t="n">
         <v>2302</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="24" t="n">
         <v>2302</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="24" t="n">
         <v>3042</v>
       </c>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -8212,15 +8892,16 @@
           <t>235367</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="24" t="n">
         <v>2952</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="24" t="n">
         <v>2952</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="24" t="n">
         <v>1867</v>
       </c>
+      <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -8228,15 +8909,16 @@
           <t>235005</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="24" t="n">
         <v>5394</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="24" t="n">
         <v>5394</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="24" t="n">
         <v>6114</v>
       </c>
+      <c r="E7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -8244,15 +8926,16 @@
           <t>235786</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="24" t="n">
         <v>580</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="24" t="n">
         <v>580</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="24" t="n">
         <v>884</v>
       </c>
+      <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -8260,15 +8943,16 @@
           <t>235922</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="24" t="n">
         <v>1954</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="24" t="n">
         <v>1954</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="24" t="n">
         <v>2831</v>
       </c>
+      <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -8276,15 +8960,16 @@
           <t>235921</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="24" t="n">
         <v>1103</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="24" t="n">
         <v>1103</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="24" t="n">
         <v>1379</v>
       </c>
+      <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -8292,15 +8977,16 @@
           <t>235920</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="24" t="n">
         <v>1514</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="24" t="n">
         <v>1514</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="24" t="n">
         <v>1952</v>
       </c>
+      <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -8308,15 +8994,16 @@
           <t>235287</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
+      <c r="B12" s="24" t="n">
         <v>4316</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="24" t="n">
         <v>4316</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="24" t="n">
         <v>4564</v>
       </c>
+      <c r="E12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -8324,15 +9011,16 @@
           <t>235253</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="24" t="n">
         <v>3425</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="24" t="n">
         <v>3113</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="24" t="n">
         <v>3032</v>
       </c>
+      <c r="E13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -8340,15 +9028,16 @@
           <t>235289</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="24" t="n">
         <v>903</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="24" t="n">
         <v>1044</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="24" t="n">
         <v>1079</v>
       </c>
+      <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -8356,15 +9045,16 @@
           <t>235448</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="24" t="n">
         <v>840</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="24" t="n">
         <v>720</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="24" t="n">
         <v>1036</v>
       </c>
+      <c r="E15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -8372,15 +9062,16 @@
           <t>235580</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="24" t="n">
         <v>971</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="24" t="n">
         <v>971</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="24" t="n">
         <v>1259</v>
       </c>
+      <c r="E16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -8388,15 +9079,16 @@
           <t>236327</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="24" t="n">
         <v>810</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="24" t="n">
         <v>598</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="24" t="n">
         <v>935</v>
       </c>
+      <c r="E17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -8404,15 +9096,16 @@
           <t>235917</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B18" s="24" t="n">
         <v>573</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="24" t="n">
         <v>573</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="24" t="n">
         <v>900</v>
       </c>
+      <c r="E18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -8420,15 +9113,16 @@
           <t>235952</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="24" t="n">
         <v>613</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="24" t="n">
         <v>613</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="24" t="n">
         <v>1105</v>
       </c>
+      <c r="E19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -8436,15 +9130,16 @@
           <t>235787</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="24" t="n">
         <v>3315</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="24" t="n">
         <v>3315</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="24" t="n">
         <v>3213</v>
       </c>
+      <c r="E20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -8452,15 +9147,16 @@
           <t>235785</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="24" t="n">
         <v>857</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="24" t="n">
         <v>857</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="24" t="n">
         <v>1084</v>
       </c>
+      <c r="E21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -8468,15 +9164,16 @@
           <t>236330</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="24" t="n">
         <v>825</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="24" t="n">
         <v>825</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="24" t="n">
         <v>995</v>
       </c>
+      <c r="E22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -8484,46 +9181,57 @@
           <t>236123</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
+      <c r="B23" s="24" t="n">
         <v>414</v>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="24" t="n">
         <v>414</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="24" t="n">
         <v>525</v>
       </c>
+      <c r="E23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>236663</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
+      <c r="B24" s="25" t="n">
         <v>481</v>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="25" t="n">
         <v>481</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="25" t="n">
         <v>2903</v>
       </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>236559</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
+      <c r="B25" s="25" t="n">
         <v>677</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="25" t="n">
         <v>522</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="25" t="n">
         <v>2839</v>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -8532,15 +9240,16 @@
           <t>236295</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="24" t="n">
         <v>1753</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="24" t="n">
         <v>1753</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="24" t="n">
         <v>1754</v>
       </c>
+      <c r="E26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -8548,15 +9257,16 @@
           <t>236341</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="24" t="n">
         <v>1733</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="24" t="n">
         <v>1733</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="24" t="n">
         <v>1753</v>
       </c>
+      <c r="E27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -8564,15 +9274,16 @@
           <t>236355</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="24" t="n">
         <v>242</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="24" t="n">
         <v>242</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="24" t="n">
         <v>454</v>
       </c>
+      <c r="E28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -8580,15 +9291,16 @@
           <t>236423</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="24" t="n">
         <v>4836</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="24" t="n">
         <v>4836</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="24" t="n">
         <v>4901</v>
       </c>
+      <c r="E29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -8596,30 +9308,36 @@
           <t>236673</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="24" t="n">
         <v>1651</v>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="24" t="n">
         <v>1651</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="24" t="n">
         <v>1816</v>
       </c>
+      <c r="E30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>236477</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
+      <c r="B31" s="25" t="n">
         <v>960</v>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="25" t="n">
         <v>960</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="25" t="n">
         <v>1033</v>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -8628,15 +9346,16 @@
           <t>236585</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="24" t="n">
         <v>1661</v>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="24" t="n">
         <v>1661</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D32" s="24" t="n">
         <v>2098</v>
       </c>
+      <c r="E32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -8644,15 +9363,16 @@
           <t>236561</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="24" t="n">
         <v>824</v>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="24" t="n">
         <v>824</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="24" t="n">
         <v>872</v>
       </c>
+      <c r="E33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -8660,15 +9380,16 @@
           <t>236550</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="24" t="n">
         <v>1387</v>
       </c>
-      <c r="C34" s="14" t="n">
+      <c r="C34" s="24" t="n">
         <v>1387</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="24" t="n">
         <v>1665</v>
       </c>
+      <c r="E34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -8676,15 +9397,16 @@
           <t>236802</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="24" t="n">
         <v>6164</v>
       </c>
-      <c r="C35" s="14" t="n">
+      <c r="C35" s="24" t="n">
         <v>6164</v>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D35" s="24" t="n">
         <v>5824</v>
       </c>
+      <c r="E35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -8692,15 +9414,16 @@
           <t>236688</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="24" t="n">
         <v>248</v>
       </c>
-      <c r="C36" s="14" t="n">
+      <c r="C36" s="24" t="n">
         <v>248</v>
       </c>
-      <c r="D36" s="14" t="n">
+      <c r="D36" s="24" t="n">
         <v>256</v>
       </c>
+      <c r="E36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -8708,15 +9431,16 @@
           <t>236822</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="24" t="n">
         <v>985</v>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C37" s="24" t="n">
         <v>985</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="24" t="n">
         <v>1259</v>
       </c>
+      <c r="E37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -8724,30 +9448,36 @@
           <t>236942</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="24" t="n">
         <v>724</v>
       </c>
-      <c r="C38" s="14" t="n">
+      <c r="C38" s="24" t="n">
         <v>724</v>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D38" s="24" t="n">
         <v>1121</v>
       </c>
+      <c r="E38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>236943</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
+      <c r="B39" s="25" t="n">
         <v>4353</v>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="25" t="n">
         <v>3695</v>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="D39" s="25" t="n">
         <v>6774</v>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -8756,15 +9486,16 @@
           <t>236869</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="24" t="n">
         <v>2876</v>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="24" t="n">
         <v>2749</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="24" t="n">
         <v>3071</v>
       </c>
+      <c r="E40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -8772,15 +9503,16 @@
           <t>237252</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
+      <c r="B41" s="24" t="n">
         <v>142</v>
       </c>
-      <c r="C41" s="14" t="n">
+      <c r="C41" s="24" t="n">
         <v>131</v>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="24" t="n">
         <v>132</v>
       </c>
+      <c r="E41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -8788,176 +9520,273 @@
           <t>237334</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
+      <c r="B42" s="24" t="n">
         <v>1219</v>
       </c>
-      <c r="C42" s="14" t="n">
+      <c r="C42" s="24" t="n">
         <v>1221</v>
       </c>
-      <c r="D42" s="14" t="n">
+      <c r="D42" s="24" t="n">
         <v>1303</v>
       </c>
+      <c r="E42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>237385</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="25" t="n">
         <v>2288</v>
       </c>
-      <c r="C43" s="14" t="n">
+      <c r="C43" s="25" t="n">
         <v>2280</v>
       </c>
-      <c r="D43" s="14" t="n">
+      <c r="D43" s="25" t="n">
         <v>3416</v>
       </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B44" s="15">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL (all 40)</t>
+        </is>
+      </c>
+      <c r="B44" s="26">
         <f>SUM(B4:B43)</f>
         <v/>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="26">
         <f>SUM(C4:C43)</f>
         <v/>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="26">
         <f>SUM(D4:D43)</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Cost accuracy by category (portfolio totals)</t>
-        </is>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>TOTAL (clean 35)</t>
+        </is>
+      </c>
+      <c r="B45" s="28">
+        <f>SUMIF(E4:E43,"&lt;&gt;YES",B4:B43)</f>
+        <v/>
+      </c>
+      <c r="C45" s="28">
+        <f>SUMIF(E4:E43,"&lt;&gt;YES",C4:C43)</f>
+        <v/>
+      </c>
+      <c r="D45" s="28">
+        <f>SUMIF(E4:E43,"&lt;&gt;YES",D4:D43)</f>
+        <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Cost accuracy by category — portfolio totals</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Actual $</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>SPOT est $</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>iQuote est $</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="n">
-        <v>12884</v>
-      </c>
-      <c r="C48" s="14" t="n">
-        <v>17949</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>12541</v>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>Actual $ (all)</t>
+        </is>
+      </c>
+      <c r="C48" s="29" t="inlineStr">
+        <is>
+          <t>SPOT est $ (all)</t>
+        </is>
+      </c>
+      <c r="D48" s="29" t="inlineStr">
+        <is>
+          <t>iQuote est $ (all)</t>
+        </is>
+      </c>
+      <c r="E48" s="29" t="inlineStr">
+        <is>
+          <t>Actual $ (clean)</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="inlineStr">
+        <is>
+          <t>SPOT est $ (clean)</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>iQuote est $ (clean)</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="n">
-        <v>20197</v>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>16918</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>10253</v>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="n">
+        <v>12884</v>
+      </c>
+      <c r="C49" s="24" t="n">
+        <v>17949</v>
+      </c>
+      <c r="D49" s="24" t="n">
+        <v>12541</v>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>10403</v>
+      </c>
+      <c r="F49" s="30" t="n">
+        <v>11885</v>
+      </c>
+      <c r="G49" s="30" t="n">
+        <v>11007</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Cutting</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="n">
-        <v>16932</v>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>14979</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>12721</v>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="n">
+        <v>20197</v>
+      </c>
+      <c r="C50" s="24" t="n">
+        <v>16918</v>
+      </c>
+      <c r="D50" s="24" t="n">
+        <v>10253</v>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>16155</v>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>14587</v>
+      </c>
+      <c r="G50" s="30" t="n">
+        <v>9452</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Handwork</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="n">
-        <v>342</v>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>2081</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>3526</v>
+          <t>Cutting</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="n">
+        <v>16932</v>
+      </c>
+      <c r="C51" s="24" t="n">
+        <v>14979</v>
+      </c>
+      <c r="D51" s="24" t="n">
+        <v>12721</v>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>15183</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <v>12126</v>
+      </c>
+      <c r="G51" s="30" t="n">
+        <v>9921</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>Handwork</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="n">
+        <v>342</v>
+      </c>
+      <c r="C52" s="24" t="n">
+        <v>2081</v>
+      </c>
+      <c r="D52" s="24" t="n">
+        <v>3526</v>
+      </c>
+      <c r="E52" s="30" t="n">
+        <v>252</v>
+      </c>
+      <c r="F52" s="30" t="n">
+        <v>1653</v>
+      </c>
+      <c r="G52" s="30" t="n">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
           <t>Die</t>
         </is>
       </c>
-      <c r="B52" s="14" t="n">
+      <c r="B53" s="24" t="n">
         <v>4474</v>
       </c>
-      <c r="C52" s="14" t="n">
+      <c r="C53" s="24" t="n">
         <v>3909</v>
       </c>
-      <c r="D52" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="D53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="30" t="n">
+        <v>3558</v>
+      </c>
+      <c r="F53" s="30" t="n">
+        <v>2529</v>
+      </c>
+      <c r="G53" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B53" s="15">
-        <f>SUM(B48:B52)</f>
+      <c r="B54" s="26">
+        <f>SUM(B49:B53)</f>
         <v/>
       </c>
-      <c r="C53" s="15">
-        <f>SUM(C48:C52)</f>
+      <c r="C54" s="26">
+        <f>SUM(C49:C53)</f>
         <v/>
       </c>
-      <c r="D53" s="15">
-        <f>SUM(D48:D52)</f>
+      <c r="D54" s="26">
+        <f>SUM(D49:D53)</f>
+        <v/>
+      </c>
+      <c r="E54" s="26">
+        <f>SUM(E49:E53)</f>
+        <v/>
+      </c>
+      <c r="F54" s="26">
+        <f>SUM(F49:F53)</f>
+        <v/>
+      </c>
+      <c r="G54" s="26">
+        <f>SUM(G49:G53)</f>
         <v/>
       </c>
     </row>
